--- a/outputs/euromillions/arithmetic_branch/branch_selector.xlsx
+++ b/outputs/euromillions/arithmetic_branch/branch_selector.xlsx
@@ -30276,7 +30276,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30369,6 +30369,6581 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>256</v>
+      </c>
+      <c r="C3">
+        <v>256</v>
+      </c>
+      <c r="D3">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>214</v>
+      </c>
+      <c r="C4">
+        <v>214</v>
+      </c>
+      <c r="D4">
+        <v>0.4953271028037383</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>207</v>
+      </c>
+      <c r="C5">
+        <v>207</v>
+      </c>
+      <c r="D5">
+        <v>0.6376811594202898</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>235</v>
+      </c>
+      <c r="C6">
+        <v>235</v>
+      </c>
+      <c r="D6">
+        <v>0.7829787234042553</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>210</v>
+      </c>
+      <c r="C7">
+        <v>210</v>
+      </c>
+      <c r="D7">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>205</v>
+      </c>
+      <c r="C8">
+        <v>205</v>
+      </c>
+      <c r="D8">
+        <v>0.7804878048780488</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>247</v>
+      </c>
+      <c r="C9">
+        <v>247</v>
+      </c>
+      <c r="D9">
+        <v>0.8744939271255061</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>211</v>
+      </c>
+      <c r="C10">
+        <v>211</v>
+      </c>
+      <c r="D10">
+        <v>0.995260663507109</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>230</v>
+      </c>
+      <c r="C11">
+        <v>230</v>
+      </c>
+      <c r="D11">
+        <v>0.3826086956521739</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>220</v>
+      </c>
+      <c r="C12">
+        <v>220</v>
+      </c>
+      <c r="D12">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>256</v>
+      </c>
+      <c r="C13">
+        <v>256</v>
+      </c>
+      <c r="D13">
+        <v>0.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F13">
+        <v>4</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>265</v>
+      </c>
+      <c r="C14">
+        <v>265</v>
+      </c>
+      <c r="D14">
+        <v>0.7849056603773585</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>238</v>
+      </c>
+      <c r="C15">
+        <v>238</v>
+      </c>
+      <c r="D15">
+        <v>0.4033613445378151</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>235</v>
+      </c>
+      <c r="C16">
+        <v>235</v>
+      </c>
+      <c r="D16">
+        <v>0.7829787234042553</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>233</v>
+      </c>
+      <c r="C17">
+        <v>233</v>
+      </c>
+      <c r="D17">
+        <v>0.9957081545064378</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>256</v>
+      </c>
+      <c r="C18">
+        <v>256</v>
+      </c>
+      <c r="D18">
+        <v>0.5</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>243</v>
+      </c>
+      <c r="C19">
+        <v>243</v>
+      </c>
+      <c r="D19">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>222</v>
+      </c>
+      <c r="C20">
+        <v>222</v>
+      </c>
+      <c r="D20">
+        <v>0.3243243243243243</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>219</v>
+      </c>
+      <c r="C21">
+        <v>219</v>
+      </c>
+      <c r="D21">
+        <v>0.6575342465753424</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>218</v>
+      </c>
+      <c r="C22">
+        <v>218</v>
+      </c>
+      <c r="D22">
+        <v>0.4954128440366973</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>273</v>
+      </c>
+      <c r="C23">
+        <v>273</v>
+      </c>
+      <c r="D23">
+        <v>0.5274725274725275</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>219</v>
+      </c>
+      <c r="C24">
+        <v>219</v>
+      </c>
+      <c r="D24">
+        <v>0.6575342465753424</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>239</v>
+      </c>
+      <c r="C25">
+        <v>239</v>
+      </c>
+      <c r="D25">
+        <v>0.99581589958159</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>247</v>
+      </c>
+      <c r="C26">
+        <v>247</v>
+      </c>
+      <c r="D26">
+        <v>0.8744939271255061</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>210</v>
+      </c>
+      <c r="C27">
+        <v>210</v>
+      </c>
+      <c r="D27">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>224</v>
+      </c>
+      <c r="C28">
+        <v>224</v>
+      </c>
+      <c r="D28">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F28">
+        <v>14</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>254</v>
+      </c>
+      <c r="C29">
+        <v>254</v>
+      </c>
+      <c r="D29">
+        <v>0.4960629921259843</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>278</v>
+      </c>
+      <c r="C30">
+        <v>278</v>
+      </c>
+      <c r="D30">
+        <v>0.4964028776978417</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>228</v>
+      </c>
+      <c r="C31">
+        <v>228</v>
+      </c>
+      <c r="D31">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>265</v>
+      </c>
+      <c r="C32">
+        <v>265</v>
+      </c>
+      <c r="D32">
+        <v>0.7849056603773585</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>251</v>
+      </c>
+      <c r="C33">
+        <v>251</v>
+      </c>
+      <c r="D33">
+        <v>0.9960159362549801</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>251</v>
+      </c>
+      <c r="C34">
+        <v>251</v>
+      </c>
+      <c r="D34">
+        <v>0.9960159362549801</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F34">
+        <v>251</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>238</v>
+      </c>
+      <c r="C35">
+        <v>238</v>
+      </c>
+      <c r="D35">
+        <v>0.4033613445378151</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>241</v>
+      </c>
+      <c r="C36">
+        <v>241</v>
+      </c>
+      <c r="D36">
+        <v>0.995850622406639</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>237</v>
+      </c>
+      <c r="C37">
+        <v>237</v>
+      </c>
+      <c r="D37">
+        <v>0.6582278481012658</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>236</v>
+      </c>
+      <c r="C38">
+        <v>236</v>
+      </c>
+      <c r="D38">
+        <v>0.4915254237288136</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>283</v>
+      </c>
+      <c r="C39">
+        <v>283</v>
+      </c>
+      <c r="D39">
+        <v>0.9964664310954063</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>239</v>
+      </c>
+      <c r="C40">
+        <v>239</v>
+      </c>
+      <c r="D40">
+        <v>0.99581589958159</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>238</v>
+      </c>
+      <c r="C41">
+        <v>238</v>
+      </c>
+      <c r="D41">
+        <v>0.4033613445378151</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>266</v>
+      </c>
+      <c r="C42">
+        <v>266</v>
+      </c>
+      <c r="D42">
+        <v>0.4060150375939849</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F42">
+        <v>14</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>222</v>
+      </c>
+      <c r="C43">
+        <v>222</v>
+      </c>
+      <c r="D43">
+        <v>0.3243243243243243</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F43">
+        <v>2</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>274</v>
+      </c>
+      <c r="C44">
+        <v>274</v>
+      </c>
+      <c r="D44">
+        <v>0.4963503649635037</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F44">
+        <v>2</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>234</v>
+      </c>
+      <c r="C45">
+        <v>234</v>
+      </c>
+      <c r="D45">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F45">
+        <v>2</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>267</v>
+      </c>
+      <c r="C46">
+        <v>267</v>
+      </c>
+      <c r="D46">
+        <v>0.6591760299625468</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F46">
+        <v>3</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>211</v>
+      </c>
+      <c r="C47">
+        <v>211</v>
+      </c>
+      <c r="D47">
+        <v>0.995260663507109</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>258</v>
+      </c>
+      <c r="C48">
+        <v>258</v>
+      </c>
+      <c r="D48">
+        <v>0.3255813953488372</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>213</v>
+      </c>
+      <c r="C49">
+        <v>213</v>
+      </c>
+      <c r="D49">
+        <v>0.6572769953051644</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F49">
+        <v>3</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>236</v>
+      </c>
+      <c r="C50">
+        <v>236</v>
+      </c>
+      <c r="D50">
+        <v>0.4915254237288136</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>222</v>
+      </c>
+      <c r="C51">
+        <v>222</v>
+      </c>
+      <c r="D51">
+        <v>0.3243243243243243</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F51">
+        <v>2</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>224</v>
+      </c>
+      <c r="C52">
+        <v>224</v>
+      </c>
+      <c r="D52">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>263</v>
+      </c>
+      <c r="C53">
+        <v>263</v>
+      </c>
+      <c r="D53">
+        <v>0.9961977186311787</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>265</v>
+      </c>
+      <c r="C54">
+        <v>265</v>
+      </c>
+      <c r="D54">
+        <v>0.7849056603773585</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>229</v>
+      </c>
+      <c r="C55">
+        <v>229</v>
+      </c>
+      <c r="D55">
+        <v>0.9956331877729258</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>233</v>
+      </c>
+      <c r="C56">
+        <v>233</v>
+      </c>
+      <c r="D56">
+        <v>0.9957081545064378</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>250</v>
+      </c>
+      <c r="C57">
+        <v>250</v>
+      </c>
+      <c r="D57">
+        <v>0.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>243</v>
+      </c>
+      <c r="C58">
+        <v>243</v>
+      </c>
+      <c r="D58">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58">
+        <v>1</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2024-12-24</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>261</v>
+      </c>
+      <c r="C59">
+        <v>261</v>
+      </c>
+      <c r="D59">
+        <v>0.6436781609195402</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F59">
+        <v>9</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>239</v>
+      </c>
+      <c r="C60">
+        <v>239</v>
+      </c>
+      <c r="D60">
+        <v>0.99581589958159</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>246</v>
+      </c>
+      <c r="C61">
+        <v>246</v>
+      </c>
+      <c r="D61">
+        <v>0.3252032520325203</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-01-03</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>255</v>
+      </c>
+      <c r="C62">
+        <v>255</v>
+      </c>
+      <c r="D62">
+        <v>0.5019607843137255</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F62">
+        <v>3</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-01-07</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>250</v>
+      </c>
+      <c r="C63">
+        <v>250</v>
+      </c>
+      <c r="D63">
+        <v>0.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F63">
+        <v>5</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>279</v>
+      </c>
+      <c r="C64">
+        <v>279</v>
+      </c>
+      <c r="D64">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>272</v>
+      </c>
+      <c r="C65">
+        <v>272</v>
+      </c>
+      <c r="D65">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65">
+        <v>1</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>283</v>
+      </c>
+      <c r="C66">
+        <v>283</v>
+      </c>
+      <c r="D66">
+        <v>0.9964664310954063</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>232</v>
+      </c>
+      <c r="C67">
+        <v>232</v>
+      </c>
+      <c r="D67">
+        <v>0.4827586206896552</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>1</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-01-24</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>272</v>
+      </c>
+      <c r="C68">
+        <v>272</v>
+      </c>
+      <c r="D68">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F68">
+        <v>8</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>241</v>
+      </c>
+      <c r="C69">
+        <v>241</v>
+      </c>
+      <c r="D69">
+        <v>0.995850622406639</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
+      </c>
+      <c r="I69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>245</v>
+      </c>
+      <c r="C70">
+        <v>245</v>
+      </c>
+      <c r="D70">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>216</v>
+      </c>
+      <c r="C71">
+        <v>216</v>
+      </c>
+      <c r="D71">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71">
+        <v>1</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-02-07</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>265</v>
+      </c>
+      <c r="C72">
+        <v>265</v>
+      </c>
+      <c r="D72">
+        <v>0.7849056603773585</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="B73">
+        <v>256</v>
+      </c>
+      <c r="C73">
+        <v>256</v>
+      </c>
+      <c r="D73">
+        <v>0.5</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>226</v>
+      </c>
+      <c r="C74">
+        <v>226</v>
+      </c>
+      <c r="D74">
+        <v>0.495575221238938</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F74">
+        <v>2</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>211</v>
+      </c>
+      <c r="C75">
+        <v>211</v>
+      </c>
+      <c r="D75">
+        <v>0.995260663507109</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="I75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>245</v>
+      </c>
+      <c r="C76">
+        <v>245</v>
+      </c>
+      <c r="D76">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="B77">
+        <v>259</v>
+      </c>
+      <c r="C77">
+        <v>259</v>
+      </c>
+      <c r="D77">
+        <v>0.833976833976834</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F77">
+        <v>7</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="B78">
+        <v>232</v>
+      </c>
+      <c r="C78">
+        <v>232</v>
+      </c>
+      <c r="D78">
+        <v>0.4827586206896552</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78">
+        <v>1</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>307</v>
+      </c>
+      <c r="C79">
+        <v>307</v>
+      </c>
+      <c r="D79">
+        <v>0.996742671009772</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="B80">
+        <v>271</v>
+      </c>
+      <c r="C80">
+        <v>271</v>
+      </c>
+      <c r="D80">
+        <v>0.996309963099631</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="B81">
+        <v>250</v>
+      </c>
+      <c r="C81">
+        <v>250</v>
+      </c>
+      <c r="D81">
+        <v>0.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="G81">
+        <v>1</v>
+      </c>
+      <c r="H81">
+        <v>1</v>
+      </c>
+      <c r="I81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="B82">
+        <v>259</v>
+      </c>
+      <c r="C82">
+        <v>259</v>
+      </c>
+      <c r="D82">
+        <v>0.833976833976834</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+      <c r="H82">
+        <v>1</v>
+      </c>
+      <c r="I82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>241</v>
+      </c>
+      <c r="C83">
+        <v>241</v>
+      </c>
+      <c r="D83">
+        <v>0.995850622406639</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F83">
+        <v>1</v>
+      </c>
+      <c r="G83">
+        <v>1</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>232</v>
+      </c>
+      <c r="C84">
+        <v>232</v>
+      </c>
+      <c r="D84">
+        <v>0.4827586206896552</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F84">
+        <v>1</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+      <c r="H84">
+        <v>1</v>
+      </c>
+      <c r="I84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>250</v>
+      </c>
+      <c r="C85">
+        <v>250</v>
+      </c>
+      <c r="D85">
+        <v>0.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F85">
+        <v>2</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>280</v>
+      </c>
+      <c r="C86">
+        <v>280</v>
+      </c>
+      <c r="D86">
+        <v>0.3428571428571429</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F86">
+        <v>10</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>255</v>
+      </c>
+      <c r="C87">
+        <v>255</v>
+      </c>
+      <c r="D87">
+        <v>0.5019607843137255</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F87">
+        <v>5</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>240</v>
+      </c>
+      <c r="C88">
+        <v>240</v>
+      </c>
+      <c r="D88">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F88">
+        <v>15</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>1</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>252</v>
+      </c>
+      <c r="C89">
+        <v>252</v>
+      </c>
+      <c r="D89">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F89">
+        <v>12</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>264</v>
+      </c>
+      <c r="C90">
+        <v>264</v>
+      </c>
+      <c r="D90">
+        <v>0.303030303030303</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F90">
+        <v>12</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>263</v>
+      </c>
+      <c r="C91">
+        <v>263</v>
+      </c>
+      <c r="D91">
+        <v>0.9961977186311787</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
+      </c>
+      <c r="I91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>303</v>
+      </c>
+      <c r="C92">
+        <v>303</v>
+      </c>
+      <c r="D92">
+        <v>0.6600660066006601</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>241</v>
+      </c>
+      <c r="C93">
+        <v>241</v>
+      </c>
+      <c r="D93">
+        <v>0.995850622406639</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+      <c r="G93">
+        <v>1</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="B94">
+        <v>245</v>
+      </c>
+      <c r="C94">
+        <v>245</v>
+      </c>
+      <c r="D94">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F94">
+        <v>1</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="B95">
+        <v>232</v>
+      </c>
+      <c r="C95">
+        <v>232</v>
+      </c>
+      <c r="D95">
+        <v>0.4827586206896552</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="G95">
+        <v>1</v>
+      </c>
+      <c r="H95">
+        <v>1</v>
+      </c>
+      <c r="I95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="B96">
+        <v>244</v>
+      </c>
+      <c r="C96">
+        <v>244</v>
+      </c>
+      <c r="D96">
+        <v>0.4918032786885246</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F96">
+        <v>4</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="B97">
+        <v>259</v>
+      </c>
+      <c r="C97">
+        <v>259</v>
+      </c>
+      <c r="D97">
+        <v>0.833976833976834</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+      <c r="H97">
+        <v>1</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="B98">
+        <v>263</v>
+      </c>
+      <c r="C98">
+        <v>263</v>
+      </c>
+      <c r="D98">
+        <v>0.9961977186311787</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="B99">
+        <v>293</v>
+      </c>
+      <c r="C99">
+        <v>293</v>
+      </c>
+      <c r="D99">
+        <v>0.9965870307167235</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="B100">
+        <v>268</v>
+      </c>
+      <c r="C100">
+        <v>268</v>
+      </c>
+      <c r="D100">
+        <v>0.4925373134328358</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+      <c r="H100">
+        <v>1</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="B101">
+        <v>242</v>
+      </c>
+      <c r="C101">
+        <v>242</v>
+      </c>
+      <c r="D101">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F101">
+        <v>2</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>237</v>
+      </c>
+      <c r="C102">
+        <v>237</v>
+      </c>
+      <c r="D102">
+        <v>0.6582278481012658</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102">
+        <v>1</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>253</v>
+      </c>
+      <c r="C103">
+        <v>253</v>
+      </c>
+      <c r="D103">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F103">
+        <v>1</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>206</v>
+      </c>
+      <c r="C104">
+        <v>206</v>
+      </c>
+      <c r="D104">
+        <v>0.4951456310679612</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F104">
+        <v>1</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="H104">
+        <v>1</v>
+      </c>
+      <c r="I104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>278</v>
+      </c>
+      <c r="C105">
+        <v>278</v>
+      </c>
+      <c r="D105">
+        <v>0.4964028776978417</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F105">
+        <v>2</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>316</v>
+      </c>
+      <c r="C106">
+        <v>316</v>
+      </c>
+      <c r="D106">
+        <v>0.4936708860759494</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F106">
+        <v>2</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>234</v>
+      </c>
+      <c r="C107">
+        <v>234</v>
+      </c>
+      <c r="D107">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F107">
+        <v>2</v>
+      </c>
+      <c r="G107">
+        <v>0</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>267</v>
+      </c>
+      <c r="C108">
+        <v>267</v>
+      </c>
+      <c r="D108">
+        <v>0.6591760299625468</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F108">
+        <v>3</v>
+      </c>
+      <c r="G108">
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <v>1</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>275</v>
+      </c>
+      <c r="C109">
+        <v>275</v>
+      </c>
+      <c r="D109">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F109">
+        <v>1</v>
+      </c>
+      <c r="G109">
+        <v>1</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>292</v>
+      </c>
+      <c r="C110">
+        <v>292</v>
+      </c>
+      <c r="D110">
+        <v>0.4931506849315068</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F110">
+        <v>1</v>
+      </c>
+      <c r="G110">
+        <v>1</v>
+      </c>
+      <c r="H110">
+        <v>1</v>
+      </c>
+      <c r="I110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>284</v>
+      </c>
+      <c r="C111">
+        <v>284</v>
+      </c>
+      <c r="D111">
+        <v>0.4929577464788732</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F111">
+        <v>4</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>249</v>
+      </c>
+      <c r="C112">
+        <v>249</v>
+      </c>
+      <c r="D112">
+        <v>0.6586345381526104</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F112">
+        <v>1</v>
+      </c>
+      <c r="G112">
+        <v>1</v>
+      </c>
+      <c r="H112">
+        <v>1</v>
+      </c>
+      <c r="I112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>241</v>
+      </c>
+      <c r="C113">
+        <v>241</v>
+      </c>
+      <c r="D113">
+        <v>0.995850622406639</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F113">
+        <v>1</v>
+      </c>
+      <c r="G113">
+        <v>1</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>296</v>
+      </c>
+      <c r="C114">
+        <v>296</v>
+      </c>
+      <c r="D114">
+        <v>0.4864864864864865</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F114">
+        <v>1</v>
+      </c>
+      <c r="G114">
+        <v>1</v>
+      </c>
+      <c r="H114">
+        <v>1</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>219</v>
+      </c>
+      <c r="C115">
+        <v>219</v>
+      </c>
+      <c r="D115">
+        <v>0.6575342465753424</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F115">
+        <v>1</v>
+      </c>
+      <c r="G115">
+        <v>1</v>
+      </c>
+      <c r="H115">
+        <v>1</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>257</v>
+      </c>
+      <c r="C116">
+        <v>257</v>
+      </c>
+      <c r="D116">
+        <v>0.9961089494163424</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
+      <c r="G116">
+        <v>1</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>239</v>
+      </c>
+      <c r="C117">
+        <v>239</v>
+      </c>
+      <c r="D117">
+        <v>0.99581589958159</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
+      <c r="G117">
+        <v>1</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>298</v>
+      </c>
+      <c r="C118">
+        <v>298</v>
+      </c>
+      <c r="D118">
+        <v>0.4966442953020134</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F118">
+        <v>1</v>
+      </c>
+      <c r="G118">
+        <v>1</v>
+      </c>
+      <c r="H118">
+        <v>1</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>237</v>
+      </c>
+      <c r="C119">
+        <v>237</v>
+      </c>
+      <c r="D119">
+        <v>0.6582278481012658</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F119">
+        <v>1</v>
+      </c>
+      <c r="G119">
+        <v>1</v>
+      </c>
+      <c r="H119">
+        <v>1</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>274</v>
+      </c>
+      <c r="C120">
+        <v>274</v>
+      </c>
+      <c r="D120">
+        <v>0.4963503649635037</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F120">
+        <v>1</v>
+      </c>
+      <c r="G120">
+        <v>1</v>
+      </c>
+      <c r="H120">
+        <v>1</v>
+      </c>
+      <c r="I120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>231</v>
+      </c>
+      <c r="C121">
+        <v>231</v>
+      </c>
+      <c r="D121">
+        <v>0.5194805194805194</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F121">
+        <v>1</v>
+      </c>
+      <c r="G121">
+        <v>1</v>
+      </c>
+      <c r="H121">
+        <v>1</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>285</v>
+      </c>
+      <c r="C122">
+        <v>285</v>
+      </c>
+      <c r="D122">
+        <v>0.5052631578947369</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F122">
+        <v>3</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>238</v>
+      </c>
+      <c r="C123">
+        <v>238</v>
+      </c>
+      <c r="D123">
+        <v>0.4033613445378151</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+      <c r="G123">
+        <v>1</v>
+      </c>
+      <c r="H123">
+        <v>1</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>291</v>
+      </c>
+      <c r="C124">
+        <v>291</v>
+      </c>
+      <c r="D124">
+        <v>0.6597938144329897</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F124">
+        <v>1</v>
+      </c>
+      <c r="G124">
+        <v>1</v>
+      </c>
+      <c r="H124">
+        <v>1</v>
+      </c>
+      <c r="I124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>305</v>
+      </c>
+      <c r="C125">
+        <v>305</v>
+      </c>
+      <c r="D125">
+        <v>0.7868852459016393</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F125">
+        <v>1</v>
+      </c>
+      <c r="G125">
+        <v>1</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>276</v>
+      </c>
+      <c r="C126">
+        <v>276</v>
+      </c>
+      <c r="D126">
+        <v>0.3188405797101449</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+      <c r="G126">
+        <v>1</v>
+      </c>
+      <c r="H126">
+        <v>1</v>
+      </c>
+      <c r="I126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>243</v>
+      </c>
+      <c r="C127">
+        <v>243</v>
+      </c>
+      <c r="D127">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F127">
+        <v>3</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>1</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>269</v>
+      </c>
+      <c r="C128">
+        <v>269</v>
+      </c>
+      <c r="D128">
+        <v>0.9962825278810409</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="G128">
+        <v>1</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>269</v>
+      </c>
+      <c r="C129">
+        <v>269</v>
+      </c>
+      <c r="D129">
+        <v>0.9962825278810409</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F129">
+        <v>269</v>
+      </c>
+      <c r="G129">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>273</v>
+      </c>
+      <c r="C130">
+        <v>273</v>
+      </c>
+      <c r="D130">
+        <v>0.5274725274725275</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F130">
+        <v>1</v>
+      </c>
+      <c r="G130">
+        <v>1</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>262</v>
+      </c>
+      <c r="C131">
+        <v>262</v>
+      </c>
+      <c r="D131">
+        <v>0.4961832061068702</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F131">
+        <v>1</v>
+      </c>
+      <c r="G131">
+        <v>1</v>
+      </c>
+      <c r="H131">
+        <v>1</v>
+      </c>
+      <c r="I131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>245</v>
+      </c>
+      <c r="C132">
+        <v>245</v>
+      </c>
+      <c r="D132">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F132">
+        <v>1</v>
+      </c>
+      <c r="G132">
+        <v>1</v>
+      </c>
+      <c r="H132">
+        <v>1</v>
+      </c>
+      <c r="I132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>280</v>
+      </c>
+      <c r="C133">
+        <v>280</v>
+      </c>
+      <c r="D133">
+        <v>0.3428571428571429</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F133">
+        <v>35</v>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>1</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>292</v>
+      </c>
+      <c r="C134">
+        <v>292</v>
+      </c>
+      <c r="D134">
+        <v>0.4931506849315068</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F134">
+        <v>4</v>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>272</v>
+      </c>
+      <c r="C135">
+        <v>272</v>
+      </c>
+      <c r="D135">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F135">
+        <v>4</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>295</v>
+      </c>
+      <c r="C136">
+        <v>295</v>
+      </c>
+      <c r="D136">
+        <v>0.7864406779661017</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+      <c r="G136">
+        <v>1</v>
+      </c>
+      <c r="H136">
+        <v>1</v>
+      </c>
+      <c r="I136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>275</v>
+      </c>
+      <c r="C137">
+        <v>275</v>
+      </c>
+      <c r="D137">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F137">
+        <v>5</v>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>263</v>
+      </c>
+      <c r="C138">
+        <v>263</v>
+      </c>
+      <c r="D138">
+        <v>0.9961977186311787</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+      <c r="G138">
+        <v>1</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>296</v>
+      </c>
+      <c r="C139">
+        <v>296</v>
+      </c>
+      <c r="D139">
+        <v>0.4864864864864865</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F139">
+        <v>1</v>
+      </c>
+      <c r="G139">
+        <v>1</v>
+      </c>
+      <c r="H139">
+        <v>1</v>
+      </c>
+      <c r="I139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>284</v>
+      </c>
+      <c r="C140">
+        <v>284</v>
+      </c>
+      <c r="D140">
+        <v>0.4929577464788732</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F140">
+        <v>4</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>276</v>
+      </c>
+      <c r="C141">
+        <v>276</v>
+      </c>
+      <c r="D141">
+        <v>0.3188405797101449</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F141">
+        <v>4</v>
+      </c>
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>258</v>
+      </c>
+      <c r="C142">
+        <v>258</v>
+      </c>
+      <c r="D142">
+        <v>0.3255813953488372</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F142">
+        <v>6</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>261</v>
+      </c>
+      <c r="C143">
+        <v>261</v>
+      </c>
+      <c r="D143">
+        <v>0.6436781609195402</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F143">
+        <v>3</v>
+      </c>
+      <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <v>1</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>279</v>
+      </c>
+      <c r="C144">
+        <v>279</v>
+      </c>
+      <c r="D144">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F144">
+        <v>9</v>
+      </c>
+      <c r="G144">
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>278</v>
+      </c>
+      <c r="C145">
+        <v>278</v>
+      </c>
+      <c r="D145">
+        <v>0.4964028776978417</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F145">
+        <v>1</v>
+      </c>
+      <c r="G145">
+        <v>1</v>
+      </c>
+      <c r="H145">
+        <v>1</v>
+      </c>
+      <c r="I145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>260</v>
+      </c>
+      <c r="C146">
+        <v>260</v>
+      </c>
+      <c r="D146">
+        <v>0.3692307692307693</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F146">
+        <v>2</v>
+      </c>
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>270</v>
+      </c>
+      <c r="C147">
+        <v>270</v>
+      </c>
+      <c r="D147">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F147">
+        <v>10</v>
+      </c>
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
+      </c>
+      <c r="I147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>270</v>
+      </c>
+      <c r="C148">
+        <v>270</v>
+      </c>
+      <c r="D148">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F148">
+        <v>270</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>259</v>
+      </c>
+      <c r="C149">
+        <v>259</v>
+      </c>
+      <c r="D149">
+        <v>0.833976833976834</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F149">
+        <v>1</v>
+      </c>
+      <c r="G149">
+        <v>1</v>
+      </c>
+      <c r="H149">
+        <v>1</v>
+      </c>
+      <c r="I149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>287</v>
+      </c>
+      <c r="C150">
+        <v>287</v>
+      </c>
+      <c r="D150">
+        <v>0.8362369337979094</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F150">
+        <v>7</v>
+      </c>
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>241</v>
+      </c>
+      <c r="C151">
+        <v>241</v>
+      </c>
+      <c r="D151">
+        <v>0.995850622406639</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F151">
+        <v>1</v>
+      </c>
+      <c r="G151">
+        <v>1</v>
+      </c>
+      <c r="H151">
+        <v>0</v>
+      </c>
+      <c r="I151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>250</v>
+      </c>
+      <c r="C152">
+        <v>250</v>
+      </c>
+      <c r="D152">
+        <v>0.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F152">
+        <v>1</v>
+      </c>
+      <c r="G152">
+        <v>1</v>
+      </c>
+      <c r="H152">
+        <v>1</v>
+      </c>
+      <c r="I152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="B153">
+        <v>264</v>
+      </c>
+      <c r="C153">
+        <v>264</v>
+      </c>
+      <c r="D153">
+        <v>0.303030303030303</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F153">
+        <v>2</v>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <v>0</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="B154">
+        <v>325</v>
+      </c>
+      <c r="C154">
+        <v>325</v>
+      </c>
+      <c r="D154">
+        <v>0.7384615384615385</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F154">
+        <v>1</v>
+      </c>
+      <c r="G154">
+        <v>1</v>
+      </c>
+      <c r="H154">
+        <v>1</v>
+      </c>
+      <c r="I154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="B155">
+        <v>303</v>
+      </c>
+      <c r="C155">
+        <v>303</v>
+      </c>
+      <c r="D155">
+        <v>0.6600660066006601</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F155">
+        <v>1</v>
+      </c>
+      <c r="G155">
+        <v>1</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+      <c r="I155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="B156">
+        <v>294</v>
+      </c>
+      <c r="C156">
+        <v>294</v>
+      </c>
+      <c r="D156">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F156">
+        <v>3</v>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>1</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="B157">
+        <v>281</v>
+      </c>
+      <c r="C157">
+        <v>281</v>
+      </c>
+      <c r="D157">
+        <v>0.99644128113879</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F157">
+        <v>1</v>
+      </c>
+      <c r="G157">
+        <v>1</v>
+      </c>
+      <c r="H157">
+        <v>1</v>
+      </c>
+      <c r="I157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>273</v>
+      </c>
+      <c r="C158">
+        <v>273</v>
+      </c>
+      <c r="D158">
+        <v>0.5274725274725275</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F158">
+        <v>1</v>
+      </c>
+      <c r="G158">
+        <v>1</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>262</v>
+      </c>
+      <c r="C159">
+        <v>262</v>
+      </c>
+      <c r="D159">
+        <v>0.4961832061068702</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F159">
+        <v>1</v>
+      </c>
+      <c r="G159">
+        <v>1</v>
+      </c>
+      <c r="H159">
+        <v>1</v>
+      </c>
+      <c r="I159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>249</v>
+      </c>
+      <c r="C160">
+        <v>249</v>
+      </c>
+      <c r="D160">
+        <v>0.6586345381526104</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F160">
+        <v>1</v>
+      </c>
+      <c r="G160">
+        <v>1</v>
+      </c>
+      <c r="H160">
+        <v>1</v>
+      </c>
+      <c r="I160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>292</v>
+      </c>
+      <c r="C161">
+        <v>292</v>
+      </c>
+      <c r="D161">
+        <v>0.4931506849315068</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F161">
+        <v>1</v>
+      </c>
+      <c r="G161">
+        <v>1</v>
+      </c>
+      <c r="H161">
+        <v>1</v>
+      </c>
+      <c r="I161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>274</v>
+      </c>
+      <c r="C162">
+        <v>274</v>
+      </c>
+      <c r="D162">
+        <v>0.4963503649635037</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F162">
+        <v>2</v>
+      </c>
+      <c r="G162">
+        <v>0</v>
+      </c>
+      <c r="H162">
+        <v>0</v>
+      </c>
+      <c r="I162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>273</v>
+      </c>
+      <c r="C163">
+        <v>273</v>
+      </c>
+      <c r="D163">
+        <v>0.5274725274725275</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F163">
+        <v>1</v>
+      </c>
+      <c r="G163">
+        <v>1</v>
+      </c>
+      <c r="H163">
+        <v>1</v>
+      </c>
+      <c r="I163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="B164">
+        <v>260</v>
+      </c>
+      <c r="C164">
+        <v>260</v>
+      </c>
+      <c r="D164">
+        <v>0.3692307692307693</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F164">
+        <v>13</v>
+      </c>
+      <c r="G164">
+        <v>0</v>
+      </c>
+      <c r="H164">
+        <v>1</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>268</v>
+      </c>
+      <c r="C165">
+        <v>268</v>
+      </c>
+      <c r="D165">
+        <v>0.4925373134328358</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F165">
+        <v>4</v>
+      </c>
+      <c r="G165">
+        <v>0</v>
+      </c>
+      <c r="H165">
+        <v>0</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>283</v>
+      </c>
+      <c r="C166">
+        <v>283</v>
+      </c>
+      <c r="D166">
+        <v>0.9964664310954063</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F166">
+        <v>1</v>
+      </c>
+      <c r="G166">
+        <v>1</v>
+      </c>
+      <c r="H166">
+        <v>1</v>
+      </c>
+      <c r="I166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>266</v>
+      </c>
+      <c r="C167">
+        <v>266</v>
+      </c>
+      <c r="D167">
+        <v>0.4060150375939849</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F167">
+        <v>1</v>
+      </c>
+      <c r="G167">
+        <v>1</v>
+      </c>
+      <c r="H167">
+        <v>1</v>
+      </c>
+      <c r="I167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B168">
+        <v>271</v>
+      </c>
+      <c r="C168">
+        <v>271</v>
+      </c>
+      <c r="D168">
+        <v>0.996309963099631</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F168">
+        <v>1</v>
+      </c>
+      <c r="G168">
+        <v>1</v>
+      </c>
+      <c r="H168">
+        <v>1</v>
+      </c>
+      <c r="I168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B169">
+        <v>286</v>
+      </c>
+      <c r="C169">
+        <v>286</v>
+      </c>
+      <c r="D169">
+        <v>0.4195804195804196</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F169">
+        <v>1</v>
+      </c>
+      <c r="G169">
+        <v>1</v>
+      </c>
+      <c r="H169">
+        <v>1</v>
+      </c>
+      <c r="I169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B170">
+        <v>283</v>
+      </c>
+      <c r="C170">
+        <v>283</v>
+      </c>
+      <c r="D170">
+        <v>0.9964664310954063</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F170">
+        <v>1</v>
+      </c>
+      <c r="G170">
+        <v>1</v>
+      </c>
+      <c r="H170">
+        <v>1</v>
+      </c>
+      <c r="I170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B171">
+        <v>218</v>
+      </c>
+      <c r="C171">
+        <v>218</v>
+      </c>
+      <c r="D171">
+        <v>0.4954128440366973</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F171">
+        <v>1</v>
+      </c>
+      <c r="G171">
+        <v>1</v>
+      </c>
+      <c r="H171">
+        <v>1</v>
+      </c>
+      <c r="I171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B172">
+        <v>297</v>
+      </c>
+      <c r="C172">
+        <v>297</v>
+      </c>
+      <c r="D172">
+        <v>0.6060606060606061</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F172">
+        <v>1</v>
+      </c>
+      <c r="G172">
+        <v>1</v>
+      </c>
+      <c r="H172">
+        <v>1</v>
+      </c>
+      <c r="I172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>299</v>
+      </c>
+      <c r="C173">
+        <v>299</v>
+      </c>
+      <c r="D173">
+        <v>0.882943143812709</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F173">
+        <v>1</v>
+      </c>
+      <c r="G173">
+        <v>1</v>
+      </c>
+      <c r="H173">
+        <v>0</v>
+      </c>
+      <c r="I173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B174">
+        <v>267</v>
+      </c>
+      <c r="C174">
+        <v>267</v>
+      </c>
+      <c r="D174">
+        <v>0.6591760299625468</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F174">
+        <v>1</v>
+      </c>
+      <c r="G174">
+        <v>1</v>
+      </c>
+      <c r="H174">
+        <v>0</v>
+      </c>
+      <c r="I174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B175">
+        <v>268</v>
+      </c>
+      <c r="C175">
+        <v>268</v>
+      </c>
+      <c r="D175">
+        <v>0.4925373134328358</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F175">
+        <v>1</v>
+      </c>
+      <c r="G175">
+        <v>1</v>
+      </c>
+      <c r="H175">
+        <v>1</v>
+      </c>
+      <c r="I175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B176">
+        <v>283</v>
+      </c>
+      <c r="C176">
+        <v>283</v>
+      </c>
+      <c r="D176">
+        <v>0.9964664310954063</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F176">
+        <v>1</v>
+      </c>
+      <c r="G176">
+        <v>1</v>
+      </c>
+      <c r="H176">
+        <v>1</v>
+      </c>
+      <c r="I176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B177">
+        <v>271</v>
+      </c>
+      <c r="C177">
+        <v>271</v>
+      </c>
+      <c r="D177">
+        <v>0.996309963099631</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F177">
+        <v>1</v>
+      </c>
+      <c r="G177">
+        <v>1</v>
+      </c>
+      <c r="H177">
+        <v>0</v>
+      </c>
+      <c r="I177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B178">
+        <v>274</v>
+      </c>
+      <c r="C178">
+        <v>274</v>
+      </c>
+      <c r="D178">
+        <v>0.4963503649635037</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F178">
+        <v>1</v>
+      </c>
+      <c r="G178">
+        <v>1</v>
+      </c>
+      <c r="H178">
+        <v>1</v>
+      </c>
+      <c r="I178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B179">
+        <v>283</v>
+      </c>
+      <c r="C179">
+        <v>283</v>
+      </c>
+      <c r="D179">
+        <v>0.9964664310954063</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F179">
+        <v>1</v>
+      </c>
+      <c r="G179">
+        <v>1</v>
+      </c>
+      <c r="H179">
+        <v>1</v>
+      </c>
+      <c r="I179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>285</v>
+      </c>
+      <c r="C180">
+        <v>285</v>
+      </c>
+      <c r="D180">
+        <v>0.5052631578947369</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F180">
+        <v>1</v>
+      </c>
+      <c r="G180">
+        <v>1</v>
+      </c>
+      <c r="H180">
+        <v>0</v>
+      </c>
+      <c r="I180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>251</v>
+      </c>
+      <c r="C181">
+        <v>251</v>
+      </c>
+      <c r="D181">
+        <v>0.9960159362549801</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F181">
+        <v>1</v>
+      </c>
+      <c r="G181">
+        <v>1</v>
+      </c>
+      <c r="H181">
+        <v>0</v>
+      </c>
+      <c r="I181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>300</v>
+      </c>
+      <c r="C182">
+        <v>300</v>
+      </c>
+      <c r="D182">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F182">
+        <v>1</v>
+      </c>
+      <c r="G182">
+        <v>1</v>
+      </c>
+      <c r="H182">
+        <v>1</v>
+      </c>
+      <c r="I182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>272</v>
+      </c>
+      <c r="C183">
+        <v>272</v>
+      </c>
+      <c r="D183">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F183">
+        <v>4</v>
+      </c>
+      <c r="G183">
+        <v>0</v>
+      </c>
+      <c r="H183">
+        <v>0</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>292</v>
+      </c>
+      <c r="C184">
+        <v>292</v>
+      </c>
+      <c r="D184">
+        <v>0.4931506849315068</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F184">
+        <v>4</v>
+      </c>
+      <c r="G184">
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B185">
+        <v>282</v>
+      </c>
+      <c r="C185">
+        <v>282</v>
+      </c>
+      <c r="D185">
+        <v>0.3262411347517731</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F185">
+        <v>2</v>
+      </c>
+      <c r="G185">
+        <v>0</v>
+      </c>
+      <c r="H185">
+        <v>0</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B186">
+        <v>247</v>
+      </c>
+      <c r="C186">
+        <v>247</v>
+      </c>
+      <c r="D186">
+        <v>0.8744939271255061</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F186">
+        <v>1</v>
+      </c>
+      <c r="G186">
+        <v>1</v>
+      </c>
+      <c r="H186">
+        <v>1</v>
+      </c>
+      <c r="I186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B187">
+        <v>281</v>
+      </c>
+      <c r="C187">
+        <v>281</v>
+      </c>
+      <c r="D187">
+        <v>0.99644128113879</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F187">
+        <v>1</v>
+      </c>
+      <c r="G187">
+        <v>1</v>
+      </c>
+      <c r="H187">
+        <v>0</v>
+      </c>
+      <c r="I187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B188">
+        <v>287</v>
+      </c>
+      <c r="C188">
+        <v>287</v>
+      </c>
+      <c r="D188">
+        <v>0.8362369337979094</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F188">
+        <v>1</v>
+      </c>
+      <c r="G188">
+        <v>1</v>
+      </c>
+      <c r="H188">
+        <v>0</v>
+      </c>
+      <c r="I188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B189">
+        <v>284</v>
+      </c>
+      <c r="C189">
+        <v>284</v>
+      </c>
+      <c r="D189">
+        <v>0.4929577464788732</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F189">
+        <v>1</v>
+      </c>
+      <c r="G189">
+        <v>1</v>
+      </c>
+      <c r="H189">
+        <v>1</v>
+      </c>
+      <c r="I189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B190">
+        <v>272</v>
+      </c>
+      <c r="C190">
+        <v>272</v>
+      </c>
+      <c r="D190">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F190">
+        <v>4</v>
+      </c>
+      <c r="G190">
+        <v>0</v>
+      </c>
+      <c r="H190">
+        <v>0</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B191">
+        <v>285</v>
+      </c>
+      <c r="C191">
+        <v>285</v>
+      </c>
+      <c r="D191">
+        <v>0.5052631578947369</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F191">
+        <v>1</v>
+      </c>
+      <c r="G191">
+        <v>1</v>
+      </c>
+      <c r="H191">
+        <v>1</v>
+      </c>
+      <c r="I191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B192">
+        <v>300</v>
+      </c>
+      <c r="C192">
+        <v>300</v>
+      </c>
+      <c r="D192">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F192">
+        <v>15</v>
+      </c>
+      <c r="G192">
+        <v>0</v>
+      </c>
+      <c r="H192">
+        <v>1</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B193">
+        <v>297</v>
+      </c>
+      <c r="C193">
+        <v>297</v>
+      </c>
+      <c r="D193">
+        <v>0.6060606060606061</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F193">
+        <v>3</v>
+      </c>
+      <c r="G193">
+        <v>0</v>
+      </c>
+      <c r="H193">
+        <v>1</v>
+      </c>
+      <c r="I193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B194">
+        <v>282</v>
+      </c>
+      <c r="C194">
+        <v>282</v>
+      </c>
+      <c r="D194">
+        <v>0.3262411347517731</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F194">
+        <v>3</v>
+      </c>
+      <c r="G194">
+        <v>0</v>
+      </c>
+      <c r="H194">
+        <v>1</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B195">
+        <v>267</v>
+      </c>
+      <c r="C195">
+        <v>267</v>
+      </c>
+      <c r="D195">
+        <v>0.6591760299625468</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F195">
+        <v>3</v>
+      </c>
+      <c r="G195">
+        <v>0</v>
+      </c>
+      <c r="H195">
+        <v>1</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B196">
+        <v>257</v>
+      </c>
+      <c r="C196">
+        <v>257</v>
+      </c>
+      <c r="D196">
+        <v>0.9961089494163424</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F196">
+        <v>1</v>
+      </c>
+      <c r="G196">
+        <v>1</v>
+      </c>
+      <c r="H196">
+        <v>0</v>
+      </c>
+      <c r="I196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B197">
+        <v>297</v>
+      </c>
+      <c r="C197">
+        <v>297</v>
+      </c>
+      <c r="D197">
+        <v>0.6060606060606061</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F197">
+        <v>1</v>
+      </c>
+      <c r="G197">
+        <v>1</v>
+      </c>
+      <c r="H197">
+        <v>0</v>
+      </c>
+      <c r="I197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B198">
+        <v>251</v>
+      </c>
+      <c r="C198">
+        <v>251</v>
+      </c>
+      <c r="D198">
+        <v>0.9960159362549801</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F198">
+        <v>1</v>
+      </c>
+      <c r="G198">
+        <v>1</v>
+      </c>
+      <c r="H198">
+        <v>0</v>
+      </c>
+      <c r="I198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>290</v>
+      </c>
+      <c r="C199">
+        <v>290</v>
+      </c>
+      <c r="D199">
+        <v>0.3862068965517241</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F199">
+        <v>1</v>
+      </c>
+      <c r="G199">
+        <v>1</v>
+      </c>
+      <c r="H199">
+        <v>1</v>
+      </c>
+      <c r="I199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B200">
+        <v>277</v>
+      </c>
+      <c r="C200">
+        <v>277</v>
+      </c>
+      <c r="D200">
+        <v>0.9963898916967509</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="F200">
+        <v>1</v>
+      </c>
+      <c r="G200">
+        <v>1</v>
+      </c>
+      <c r="H200">
+        <v>1</v>
+      </c>
+      <c r="I200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>284</v>
+      </c>
+      <c r="C201">
+        <v>284</v>
+      </c>
+      <c r="D201">
+        <v>0.4929577464788732</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="F201">
+        <v>1</v>
+      </c>
+      <c r="G201">
+        <v>1</v>
+      </c>
+      <c r="H201">
+        <v>1</v>
+      </c>
+      <c r="I201">
+        <v>1</v>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="K201">
+        <v>279</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
